--- a/excel/templates/XoL_Control.xlsx
+++ b/excel/templates/XoL_Control.xlsx
@@ -1217,7 +1217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2244,7 +2244,7 @@
       <c r="E41" s="5" t="inlineStr"/>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Stop loss: minimum CoV of the attritional loss ratio [required]</t>
+          <t>Stop loss: minimum CoV of the attritional cost per life [required]</t>
         </is>
       </c>
       <c r="G41" s="6" t="n"/>
@@ -2252,24 +2252,28 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>net_claims_budget</t>
+          <t>sl_attritional_dist</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Cedant impact</t>
-        </is>
-      </c>
-      <c r="C42" s="6" t="n"/>
-      <c r="D42" s="5" t="inlineStr">
-        <is>
-          <t>quote ccy</t>
-        </is>
-      </c>
-      <c r="E42" s="5" t="inlineStr"/>
+          <t>Stochastic</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>LOGNORMAL</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr"/>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>LOGNORMAL,NORMAL</t>
+        </is>
+      </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>Blank = best-estimate gross claims</t>
+          <t>Stop loss: distribution of the attritional cost per life [required]</t>
         </is>
       </c>
       <c r="G42" s="6" t="n"/>
@@ -2277,7 +2281,7 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>reference_lives</t>
+          <t>net_claims_budget</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
@@ -2288,13 +2292,13 @@
       <c r="C43" s="6" t="n"/>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>lives</t>
+          <t>quote ccy</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr"/>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Blank = expected lives for the quote year</t>
+          <t>Blank = best-estimate gross claims</t>
         </is>
       </c>
       <c r="G43" s="6" t="n"/>
@@ -2302,7 +2306,7 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>return_periods</t>
+          <t>reference_lives</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
@@ -2310,20 +2314,16 @@
           <t>Cedant impact</t>
         </is>
       </c>
-      <c r="C44" s="6" t="inlineStr">
-        <is>
-          <t>5,50,250</t>
-        </is>
-      </c>
+      <c r="C44" s="6" t="n"/>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>years</t>
+          <t>lives</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr"/>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>Return periods shown in Exhibit C2 [required]</t>
+          <t>Blank = expected lives for the quote year</t>
         </is>
       </c>
       <c r="G44" s="6" t="n"/>
@@ -2331,37 +2331,66 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
+          <t>return_periods</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Cedant impact</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>5,50,250</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr"/>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>Return periods shown in Exhibit C2 [required]</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
           <t>currency_display</t>
         </is>
       </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="B46" s="5" t="inlineStr">
         <is>
           <t>Cedant impact</t>
         </is>
       </c>
-      <c r="C45" s="6" t="inlineStr">
+      <c r="C46" s="6" t="inlineStr">
         <is>
           <t>QUOTE</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr"/>
-      <c r="E45" s="5" t="inlineStr">
+      <c r="D46" s="5" t="inlineStr"/>
+      <c r="E46" s="5" t="inlineStr">
         <is>
           <t>QUOTE,USD</t>
         </is>
       </c>
-      <c r="F45" s="5" t="inlineStr">
+      <c r="F46" s="5" t="inlineStr">
         <is>
           <t>Currency of the client exhibits [required]</t>
         </is>
       </c>
-      <c r="G45" s="6" t="n"/>
+      <c r="G46" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:G2"/>
   </mergeCells>
-  <dataValidations count="10">
+  <dataValidations count="11">
     <dataValidation sqref="C13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"L,C,E"</formula1>
     </dataValidation>
@@ -2389,7 +2418,10 @@
     <dataValidation sqref="C39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"POISSON,NEGBIN"</formula1>
     </dataValidation>
-    <dataValidation sqref="C45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"LOGNORMAL,NORMAL"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C46" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"QUOTE,USD"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2747,7 +2779,7 @@
     <row r="2" ht="48" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>CAVEAT: portfolio-level development factors are driven by high-frequency, low-severity claims and may UNDERSTATE development above an attachment point (later reporting, case-estimate movement, slower settlement). Prefer large-claim development or a case review; state the basis. indicated_factor is written by Alteryx (reference only).</t>
+          <t>CAVEAT: portfolio-level development factors are driven by high-frequency, low-severity claims and may UNDERSTATE development above an attachment point (later reporting, case-estimate movement, slower settlement). Prefer large-claim development or a case review; state the basis. ATTRITIONAL: completion of total claims below the stop-loss large threshold (aggregate development, unearned and unwritten), used by the stop-loss attritional model only. indicated_factor is written by Alteryx (reference only).</t>
         </is>
       </c>
     </row>
@@ -2842,7 +2874,7 @@
       <formula1>"IBNR,UNEARNED,UNWRITTEN"</formula1>
     </dataValidation>
     <dataValidation sqref="C5:C54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"PRE_AP,POST_AP_AMOUNT,POST_AP_COUNT"</formula1>
+      <formula1>"PRE_AP,POST_AP_AMOUNT,POST_AP_COUNT,ATTRITIONAL"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/excel/templates/XoL_Control.xlsx
+++ b/excel/templates/XoL_Control.xlsx
@@ -583,7 +583,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>EvScenarios: Per-event deterministic scenarios</t>
+          <t>EvScenarios: Per-event scenarios</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
     <row r="2" ht="48" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>SUPPLIED uses event_id from the data; CLUSTER groups claims of the same group key whose admissions fall within window_days.</t>
+          <t>SUPPLIED uses event_id from the data only. CLUSTER also groups accident-coded claim lines (cause_code present, no event_id) of the same group key and cause whose admission (else treatment) dates fall within window_days of the cluster's first date. Events need at least min_lives lives.</t>
         </is>
       </c>
     </row>
@@ -717,14 +717,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Per-event deterministic scenarios</t>
+          <t>Per-event scenarios</t>
         </is>
       </c>
     </row>
     <row r="2" ht="48" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Lives x cost per life; return period for context.</t>
+          <t>Lives x cost per life (quote-year money). Shown deterministically against every EV option; with a return period they are also simulated (Poisson, 1 / return period) when ev_freq_source is SCENARIOS or BOTH.</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
     <row r="2" ht="48" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Scenario 0 is the best estimate (implicit). Each row overrides one input: SET replaces, ADD adds, MULT multiplies. target_key filters rows of the target table (ALL, or column=value).</t>
+          <t>Scenario 0 is the best estimate (implicit). Set Params scenario_id to run one scenario. Each row overrides one numeric column: SET replaces, MULT multiplies (&gt; 0), ADD adds; applied in that order. target_key: ALL, or column=value (Params: param_id=&lt;id&gt;, column value).</t>
         </is>
       </c>
     </row>
@@ -1201,7 +1201,7 @@
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="C5:C54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Trend,Completion,Weights,Params,FX"</formula1>
+      <formula1>"Trend,Completion,Weights,Params,FX,Layers,EvScenarios"</formula1>
     </dataValidation>
     <dataValidation sqref="F5:F54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"SET,ADD,MULT"</formula1>
@@ -1217,7 +1217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1467,28 +1467,20 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>source_mode</t>
+          <t>scenario_id</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Mode</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n"/>
       <c r="D13" s="5" t="inlineStr"/>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>L,C,E</t>
-        </is>
-      </c>
+      <c r="E13" s="5" t="inlineStr"/>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>L = standalone line data, C = claimant listing, E = ETE extension [required]</t>
+          <t>Sensitivity run: apply the Scenarios rows with this id (blank or 0 = best estimate)</t>
         </is>
       </c>
       <c r="G13" s="6" t="n"/>
@@ -1496,7 +1488,7 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>premium_basis</t>
+          <t>source_mode</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -1506,18 +1498,18 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>GROSS</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr"/>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>GROSS,GROSSNET,NET</t>
+          <t>L,C,E</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>Premium basis for rates and EPI [required]</t>
+          <t>L = standalone line data, C = claimant listing, E = ETE extension [required]</t>
         </is>
       </c>
       <c r="G14" s="6" t="n"/>
@@ -1525,7 +1517,7 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>segment_field</t>
+          <t>premium_basis</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -1535,14 +1527,18 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>segment</t>
+          <t>GROSS</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr"/>
-      <c r="E15" s="5" t="inlineStr"/>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>GROSS,GROSSNET,NET</t>
+        </is>
+      </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>Segmentation field (ETE: dim_life attribute)</t>
+          <t>Premium basis for rates and EPI [required]</t>
         </is>
       </c>
       <c r="G15" s="6" t="n"/>
@@ -1550,7 +1546,7 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>ete_tpa_filter</t>
+          <t>segment_field</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -1558,12 +1554,16 @@
           <t>Mode</t>
         </is>
       </c>
-      <c r="C16" s="6" t="n"/>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>segment</t>
+        </is>
+      </c>
       <c r="D16" s="5" t="inlineStr"/>
       <c r="E16" s="5" t="inlineStr"/>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>ETE only: comma list of TPAs to include (blank = all)</t>
+          <t>Segmentation field (ETE: dim_life attribute)</t>
         </is>
       </c>
       <c r="G16" s="6" t="n"/>
@@ -1571,28 +1571,20 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>treaty_basis</t>
+          <t>ete_tpa_filter</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Basis</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>RA</t>
-        </is>
-      </c>
+          <t>Mode</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n"/>
       <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>RA,LO</t>
-        </is>
-      </c>
+      <c r="E17" s="5" t="inlineStr"/>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>Risks attaching or losses occurring [required]</t>
+          <t>ETE only: comma list of TPAs to include (blank = all)</t>
         </is>
       </c>
       <c r="G17" s="6" t="n"/>
@@ -1600,7 +1592,7 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>claims_trigger</t>
+          <t>treaty_basis</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -1610,18 +1602,18 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>INCURRED</t>
+          <t>RA</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr"/>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>INCURRED,PAID</t>
+          <t>RA,LO</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>Claims date trigger [required]</t>
+          <t>Risks attaching or losses occurring [required]</t>
         </is>
       </c>
       <c r="G18" s="6" t="n"/>
@@ -1629,7 +1621,7 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>paid_runoff_months</t>
+          <t>claims_trigger</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -1637,16 +1629,20 @@
           <t>Basis</t>
         </is>
       </c>
-      <c r="C19" s="6" t="n"/>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>months</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr"/>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>INCURRED</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr"/>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>INCURRED,PAID</t>
+        </is>
+      </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>Paid trigger only: months after treaty year end</t>
+          <t>Claims date trigger [required]</t>
         </is>
       </c>
       <c r="G19" s="6" t="n"/>
@@ -1654,7 +1650,7 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>pp_accumulation</t>
+          <t>paid_runoff_months</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -1662,20 +1658,16 @@
           <t>Basis</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>POLICY_YEAR</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr"/>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>POLICY_YEAR,TREATY_YEAR</t>
-        </is>
-      </c>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>months</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr"/>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>Per-person accumulation period [required]</t>
+          <t>Paid trigger only: months after treaty year end</t>
         </is>
       </c>
       <c r="G20" s="6" t="n"/>
@@ -1683,24 +1675,28 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>epi_quote_year</t>
+          <t>pp_accumulation</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Exposure</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="n"/>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>quote ccy</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr"/>
+          <t>Basis</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>POLICY_YEAR</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr"/>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>POLICY_YEAR,TREATY_YEAR</t>
+        </is>
+      </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>Expected premium income for the quote year [required]</t>
+          <t>Per-person accumulation period [required]</t>
         </is>
       </c>
       <c r="G21" s="6" t="n"/>
@@ -1708,7 +1704,7 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>expected_lives_quote_year</t>
+          <t>epi_quote_year</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -1719,13 +1715,13 @@
       <c r="C22" s="6" t="n"/>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>lives</t>
+          <t>quote ccy</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr"/>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>Blank = EPI / trended average premium</t>
+          <t>Expected premium income for the quote year [required]</t>
         </is>
       </c>
       <c r="G22" s="6" t="n"/>
@@ -1733,24 +1729,24 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>years_included</t>
+          <t>expected_lives_quote_year</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Exposure</t>
         </is>
       </c>
       <c r="C23" s="6" t="n"/>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>years</t>
+          <t>lives</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr"/>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>Experience years used (comma list, 2-5 years) [required]</t>
+          <t>Blank = EPI / trended average premium</t>
         </is>
       </c>
       <c r="G23" s="6" t="n"/>
@@ -1758,7 +1754,7 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>output_threshold_pct_min_ap</t>
+          <t>years_included</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -1766,20 +1762,16 @@
           <t>Data</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
+      <c r="C24" s="6" t="n"/>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>years</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr"/>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>Write claimant rows above this % of the lowest AP [required]</t>
+          <t>Experience years used (comma list, 2-5 years) [required]</t>
         </is>
       </c>
       <c r="G24" s="6" t="n"/>
@@ -1787,7 +1779,7 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>policy_limit</t>
+          <t>output_threshold_pct_min_ap</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -1795,16 +1787,20 @@
           <t>Data</t>
         </is>
       </c>
-      <c r="C25" s="6" t="n"/>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>quote ccy</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr"/>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>Overall per-person policy limit (blank = none)</t>
+          <t>Write claimant rows above this % of the lowest AP [required]</t>
         </is>
       </c>
       <c r="G25" s="6" t="n"/>
@@ -1812,28 +1808,24 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>outlier_method</t>
+          <t>policy_limit</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Outliers</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>IQR</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr"/>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>VALUE,IQR,NONE</t>
-        </is>
-      </c>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>quote ccy</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr"/>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>Outlier threshold rule [required]</t>
+          <t>Overall per-person policy limit (blank = none)</t>
         </is>
       </c>
       <c r="G26" s="6" t="n"/>
@@ -1841,7 +1833,7 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>outlier_value</t>
+          <t>outlier_method</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -1849,16 +1841,20 @@
           <t>Outliers</t>
         </is>
       </c>
-      <c r="C27" s="6" t="n"/>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>quote ccy</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr"/>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>IQR</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr"/>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>VALUE,IQR,NONE</t>
+        </is>
+      </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>Threshold when outlier_method = VALUE</t>
+          <t>Outlier threshold rule [required]</t>
         </is>
       </c>
       <c r="G27" s="6" t="n"/>
@@ -1866,7 +1862,7 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>iqr_multiplier</t>
+          <t>outlier_value</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
@@ -1874,20 +1870,16 @@
           <t>Outliers</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
+      <c r="C28" s="6" t="n"/>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>quote ccy</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr"/>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>Multiplier when outlier_method = IQR</t>
+          <t>Threshold when outlier_method = VALUE</t>
         </is>
       </c>
       <c r="G28" s="6" t="n"/>
@@ -1895,28 +1887,28 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>full_cred_n</t>
+          <t>iqr_multiplier</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Credibility</t>
+          <t>Outliers</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>claims</t>
+          <t>x</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr"/>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>Claims for full credibility (workshop default 64) [required]</t>
+          <t>Multiplier when outlier_method = IQR</t>
         </is>
       </c>
       <c r="G29" s="6" t="n"/>
@@ -1924,7 +1916,7 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>complement_source</t>
+          <t>full_cred_n</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
@@ -1934,18 +1926,18 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>STOCHASTIC</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>STOCHASTIC,BENCHMARK,EXPIRING</t>
-        </is>
-      </c>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>claims</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr"/>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>Credibility complement [required]</t>
+          <t>Claims for full credibility (workshop default 64) [required]</t>
         </is>
       </c>
       <c r="G30" s="6" t="n"/>
@@ -1953,7 +1945,7 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>benchmark_rate</t>
+          <t>complement_source</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
@@ -1961,16 +1953,20 @@
           <t>Credibility</t>
         </is>
       </c>
-      <c r="C31" s="6" t="n"/>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>quote ccy pppy</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr"/>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>STOCHASTIC</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr"/>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>STOCHASTIC,BENCHMARK,EXPIRING</t>
+        </is>
+      </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>When complement_source = BENCHMARK</t>
+          <t>Credibility complement [required]</t>
         </is>
       </c>
       <c r="G31" s="6" t="n"/>
@@ -1978,28 +1974,24 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>incidence_adj</t>
+          <t>benchmark_rate</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Incidence</t>
-        </is>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Credibility</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="n"/>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>quote ccy pppy</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr"/>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>Overall incidence adjustment (1 = none); justify [required]</t>
+          <t>When complement_source = BENCHMARK</t>
         </is>
       </c>
       <c r="G32" s="6" t="n"/>
@@ -2007,12 +1999,12 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>qs_cedant_retention_pct</t>
+          <t>incidence_adj</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>QS</t>
+          <t>Incidence</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
@@ -2022,13 +2014,13 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>x</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr"/>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Cedant retention under an existing QS (1 = no QS) [required]</t>
+          <t>Overall incidence adjustment (1 = none); justify [required]</t>
         </is>
       </c>
       <c r="G33" s="6" t="n"/>
@@ -2036,28 +2028,28 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>evaluate_mode</t>
+          <t>qs_cedant_retention_pct</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Programme</t>
+          <t>QS</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>STANDALONE</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr"/>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>STANDALONE,PROGRAMME</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr"/>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>Options standalone, or stacked per Programme [required]</t>
+          <t>Cedant retention under an existing QS (1 = no QS) [required]</t>
         </is>
       </c>
       <c r="G34" s="6" t="n"/>
@@ -2065,28 +2057,28 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>iterations</t>
+          <t>evaluate_mode</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Stochastic</t>
+          <t>Programme</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>10000</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="inlineStr"/>
+          <t>STANDALONE</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr"/>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>STANDALONE,PROGRAMME</t>
+        </is>
+      </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Simulation iterations [required]</t>
+          <t>Options standalone, or stacked per Programme [required]</t>
         </is>
       </c>
       <c r="G35" s="6" t="n"/>
@@ -2094,7 +2086,7 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>iterations</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
@@ -2104,14 +2096,18 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>12345</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr"/>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
       <c r="E36" s="5" t="inlineStr"/>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>Random seed (recorded in the run log) [required]</t>
+          <t>Simulation iterations [required]</t>
         </is>
       </c>
       <c r="G36" s="6" t="n"/>
@@ -2119,7 +2115,7 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>fit_cutoff</t>
+          <t>seed</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
@@ -2127,16 +2123,16 @@
           <t>Stochastic</t>
         </is>
       </c>
-      <c r="C37" s="6" t="n"/>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>quote ccy</t>
-        </is>
-      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>12345</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr"/>
       <c r="E37" s="5" t="inlineStr"/>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>Severity fitting cut-off (blank = AP)</t>
+          <t>Random seed (recorded in the run log) [required]</t>
         </is>
       </c>
       <c r="G37" s="6" t="n"/>
@@ -2144,7 +2140,7 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>fit_candidates</t>
+          <t>fit_cutoff</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
@@ -2152,16 +2148,16 @@
           <t>Stochastic</t>
         </is>
       </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>LOGNORMAL,GAMMA,WEIBULL,PARETO,GPD</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="inlineStr"/>
+      <c r="C38" s="6" t="n"/>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>quote ccy</t>
+        </is>
+      </c>
       <c r="E38" s="5" t="inlineStr"/>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>Candidate severity distributions [required]</t>
+          <t>Severity fitting cut-off (blank = AP)</t>
         </is>
       </c>
       <c r="G38" s="6" t="n"/>
@@ -2169,7 +2165,7 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>freq_model</t>
+          <t>fit_candidates</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
@@ -2179,18 +2175,14 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>POISSON</t>
+          <t>LOGNORMAL,GAMMA,WEIBULL,PARETO,GPD</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr"/>
-      <c r="E39" s="5" t="inlineStr">
-        <is>
-          <t>POISSON,NEGBIN</t>
-        </is>
-      </c>
+      <c r="E39" s="5" t="inlineStr"/>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>Frequency distribution [required]</t>
+          <t>Candidate severity distributions [required]</t>
         </is>
       </c>
       <c r="G39" s="6" t="n"/>
@@ -2198,7 +2190,7 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>sl_attritional_threshold</t>
+          <t>freq_model</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
@@ -2208,18 +2200,18 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>100000</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="inlineStr">
-        <is>
-          <t>quote ccy</t>
-        </is>
-      </c>
-      <c r="E40" s="5" t="inlineStr"/>
+          <t>POISSON</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr"/>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>POISSON,NEGBIN</t>
+        </is>
+      </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>Stop loss: attritional / large split [required]</t>
+          <t>Frequency distribution [required]</t>
         </is>
       </c>
       <c r="G40" s="6" t="n"/>
@@ -2227,7 +2219,7 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>sl_cov_floor</t>
+          <t>ev_freq_source</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
@@ -2237,14 +2229,18 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>BOTH</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr"/>
-      <c r="E41" s="5" t="inlineStr"/>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>EXPERIENCE,SCENARIOS,BOTH</t>
+        </is>
+      </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Stop loss: minimum CoV of the attritional cost per life [required]</t>
+          <t>Per-event simulation: historical events, EvScenarios (with a return period), or both [required]</t>
         </is>
       </c>
       <c r="G41" s="6" t="n"/>
@@ -2252,7 +2248,7 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>sl_attritional_dist</t>
+          <t>sl_attritional_threshold</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
@@ -2262,18 +2258,18 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>LOGNORMAL</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="inlineStr"/>
-      <c r="E42" s="5" t="inlineStr">
-        <is>
-          <t>LOGNORMAL,NORMAL</t>
-        </is>
-      </c>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>quote ccy</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr"/>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>Stop loss: distribution of the attritional cost per life [required]</t>
+          <t>Stop loss: attritional / large split [required]</t>
         </is>
       </c>
       <c r="G42" s="6" t="n"/>
@@ -2281,24 +2277,24 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>net_claims_budget</t>
+          <t>sl_cov_floor</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Cedant impact</t>
-        </is>
-      </c>
-      <c r="C43" s="6" t="n"/>
-      <c r="D43" s="5" t="inlineStr">
-        <is>
-          <t>quote ccy</t>
-        </is>
-      </c>
+          <t>Stochastic</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr"/>
       <c r="E43" s="5" t="inlineStr"/>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Blank = best-estimate gross claims</t>
+          <t>Stop loss: minimum CoV of the attritional cost per life [required]</t>
         </is>
       </c>
       <c r="G43" s="6" t="n"/>
@@ -2306,24 +2302,28 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>reference_lives</t>
+          <t>sl_attritional_dist</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Cedant impact</t>
-        </is>
-      </c>
-      <c r="C44" s="6" t="n"/>
-      <c r="D44" s="5" t="inlineStr">
-        <is>
-          <t>lives</t>
-        </is>
-      </c>
-      <c r="E44" s="5" t="inlineStr"/>
+          <t>Stochastic</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>LOGNORMAL</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr"/>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>LOGNORMAL,NORMAL</t>
+        </is>
+      </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>Blank = expected lives for the quote year</t>
+          <t>Stop loss: distribution of the attritional cost per life [required]</t>
         </is>
       </c>
       <c r="G44" s="6" t="n"/>
@@ -2331,7 +2331,7 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>return_periods</t>
+          <t>net_claims_budget</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
@@ -2339,20 +2339,16 @@
           <t>Cedant impact</t>
         </is>
       </c>
-      <c r="C45" s="6" t="inlineStr">
-        <is>
-          <t>5,50,250</t>
-        </is>
-      </c>
+      <c r="C45" s="6" t="n"/>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>years</t>
+          <t>quote ccy</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr"/>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>Return periods shown in Exhibit C2 [required]</t>
+          <t>Blank = best-estimate gross claims</t>
         </is>
       </c>
       <c r="G45" s="6" t="n"/>
@@ -2360,68 +2356,125 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
+          <t>reference_lives</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Cedant impact</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="n"/>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>lives</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr"/>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>Blank = expected lives for the quote year</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>return_periods</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Cedant impact</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>5,50,250</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr"/>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>Return periods shown in Exhibit C2 [required]</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
           <t>currency_display</t>
         </is>
       </c>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>Cedant impact</t>
         </is>
       </c>
-      <c r="C46" s="6" t="inlineStr">
+      <c r="C48" s="6" t="inlineStr">
         <is>
           <t>QUOTE</t>
         </is>
       </c>
-      <c r="D46" s="5" t="inlineStr"/>
-      <c r="E46" s="5" t="inlineStr">
+      <c r="D48" s="5" t="inlineStr"/>
+      <c r="E48" s="5" t="inlineStr">
         <is>
           <t>QUOTE,USD</t>
         </is>
       </c>
-      <c r="F46" s="5" t="inlineStr">
+      <c r="F48" s="5" t="inlineStr">
         <is>
           <t>Currency of the client exhibits [required]</t>
         </is>
       </c>
-      <c r="G46" s="6" t="n"/>
+      <c r="G48" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:G2"/>
   </mergeCells>
-  <dataValidations count="11">
-    <dataValidation sqref="C13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+  <dataValidations count="12">
+    <dataValidation sqref="C14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"L,C,E"</formula1>
     </dataValidation>
-    <dataValidation sqref="C14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"GROSS,GROSSNET,NET"</formula1>
     </dataValidation>
-    <dataValidation sqref="C17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"RA,LO"</formula1>
     </dataValidation>
-    <dataValidation sqref="C18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"INCURRED,PAID"</formula1>
     </dataValidation>
-    <dataValidation sqref="C20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"POLICY_YEAR,TREATY_YEAR"</formula1>
     </dataValidation>
-    <dataValidation sqref="C26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"VALUE,IQR,NONE"</formula1>
     </dataValidation>
-    <dataValidation sqref="C30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"STOCHASTIC,BENCHMARK,EXPIRING"</formula1>
     </dataValidation>
-    <dataValidation sqref="C34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"STANDALONE,PROGRAMME"</formula1>
     </dataValidation>
-    <dataValidation sqref="C39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"POISSON,NEGBIN"</formula1>
     </dataValidation>
-    <dataValidation sqref="C42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"EXPERIENCE,SCENARIOS,BOTH"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"LOGNORMAL,NORMAL"</formula1>
     </dataValidation>
-    <dataValidation sqref="C46" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"QUOTE,USD"</formula1>
     </dataValidation>
   </dataValidations>

--- a/excel/templates/XoL_Control.xlsx
+++ b/excel/templates/XoL_Control.xlsx
@@ -1217,7 +1217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2190,7 +2190,7 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>freq_model</t>
+          <t>fit_selected</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
@@ -2198,20 +2198,16 @@
           <t>Stochastic</t>
         </is>
       </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>POISSON</t>
-        </is>
-      </c>
+      <c r="C40" s="6" t="n"/>
       <c r="D40" s="5" t="inlineStr"/>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>POISSON,NEGBIN</t>
+          <t>LOGNORMAL,GAMMA,WEIBULL,PARETO,GPD</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>Frequency distribution [required]</t>
+          <t>Severity distribution used by the simulation (blank = lowest AIC in stage 04a); justify an override</t>
         </is>
       </c>
       <c r="G40" s="6" t="n"/>
@@ -2219,7 +2215,7 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>ev_freq_source</t>
+          <t>severity_source</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
@@ -2229,18 +2225,18 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>BOTH</t>
+          <t>PYTHON</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr"/>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>EXPERIENCE,SCENARIOS,BOTH</t>
+          <t>PYTHON,NATIVE</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Per-event simulation: historical events, EvScenarios (with a return period), or both [required]</t>
+          <t>PYTHON: distribution selected in 04a_fit_severity (Python tool); NATIVE: Pareto fitted in stage 04 (no Python) [required]</t>
         </is>
       </c>
       <c r="G41" s="6" t="n"/>
@@ -2248,7 +2244,7 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>sl_attritional_threshold</t>
+          <t>freq_model</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
@@ -2258,18 +2254,18 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>100000</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="inlineStr">
-        <is>
-          <t>quote ccy</t>
-        </is>
-      </c>
-      <c r="E42" s="5" t="inlineStr"/>
+          <t>POISSON</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr"/>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>POISSON,NEGBIN</t>
+        </is>
+      </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>Stop loss: attritional / large split [required]</t>
+          <t>Frequency distribution [required]</t>
         </is>
       </c>
       <c r="G42" s="6" t="n"/>
@@ -2277,7 +2273,7 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>sl_cov_floor</t>
+          <t>ev_freq_source</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
@@ -2287,14 +2283,18 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>BOTH</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr"/>
-      <c r="E43" s="5" t="inlineStr"/>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>EXPERIENCE,SCENARIOS,BOTH</t>
+        </is>
+      </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Stop loss: minimum CoV of the attritional cost per life [required]</t>
+          <t>Per-event simulation: historical events, EvScenarios (with a return period), or both [required]</t>
         </is>
       </c>
       <c r="G43" s="6" t="n"/>
@@ -2302,7 +2302,7 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>sl_attritional_dist</t>
+          <t>sl_attritional_threshold</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
@@ -2312,18 +2312,18 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>LOGNORMAL</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="inlineStr"/>
-      <c r="E44" s="5" t="inlineStr">
-        <is>
-          <t>LOGNORMAL,NORMAL</t>
-        </is>
-      </c>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>quote ccy</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr"/>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>Stop loss: distribution of the attritional cost per life [required]</t>
+          <t>Stop loss: attritional / large split [required]</t>
         </is>
       </c>
       <c r="G44" s="6" t="n"/>
@@ -2331,24 +2331,24 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>net_claims_budget</t>
+          <t>sl_cov_floor</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Cedant impact</t>
-        </is>
-      </c>
-      <c r="C45" s="6" t="n"/>
-      <c r="D45" s="5" t="inlineStr">
-        <is>
-          <t>quote ccy</t>
-        </is>
-      </c>
+          <t>Stochastic</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr"/>
       <c r="E45" s="5" t="inlineStr"/>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>Blank = best-estimate gross claims</t>
+          <t>Stop loss: minimum CoV of the attritional cost per life [required]</t>
         </is>
       </c>
       <c r="G45" s="6" t="n"/>
@@ -2356,24 +2356,28 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>reference_lives</t>
+          <t>sl_attritional_dist</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>Cedant impact</t>
-        </is>
-      </c>
-      <c r="C46" s="6" t="n"/>
-      <c r="D46" s="5" t="inlineStr">
-        <is>
-          <t>lives</t>
-        </is>
-      </c>
-      <c r="E46" s="5" t="inlineStr"/>
+          <t>Stochastic</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>LOGNORMAL</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr"/>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>LOGNORMAL,NORMAL</t>
+        </is>
+      </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>Blank = expected lives for the quote year</t>
+          <t>Stop loss: distribution of the attritional cost per life [required]</t>
         </is>
       </c>
       <c r="G46" s="6" t="n"/>
@@ -2381,7 +2385,7 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>return_periods</t>
+          <t>net_claims_budget</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
@@ -2389,20 +2393,16 @@
           <t>Cedant impact</t>
         </is>
       </c>
-      <c r="C47" s="6" t="inlineStr">
-        <is>
-          <t>5,50,250</t>
-        </is>
-      </c>
+      <c r="C47" s="6" t="n"/>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>years</t>
+          <t>quote ccy</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr"/>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>Return periods shown in Exhibit C2 [required]</t>
+          <t>Blank = best-estimate gross claims</t>
         </is>
       </c>
       <c r="G47" s="6" t="n"/>
@@ -2410,37 +2410,91 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
+          <t>reference_lives</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>Cedant impact</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="n"/>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>lives</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr"/>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>Blank = expected lives for the quote year</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>return_periods</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Cedant impact</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>5,50,250</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr"/>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>Return periods shown in Exhibit C2 [required]</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
           <t>currency_display</t>
         </is>
       </c>
-      <c r="B48" s="5" t="inlineStr">
+      <c r="B50" s="5" t="inlineStr">
         <is>
           <t>Cedant impact</t>
         </is>
       </c>
-      <c r="C48" s="6" t="inlineStr">
+      <c r="C50" s="6" t="inlineStr">
         <is>
           <t>QUOTE</t>
         </is>
       </c>
-      <c r="D48" s="5" t="inlineStr"/>
-      <c r="E48" s="5" t="inlineStr">
+      <c r="D50" s="5" t="inlineStr"/>
+      <c r="E50" s="5" t="inlineStr">
         <is>
           <t>QUOTE,USD</t>
         </is>
       </c>
-      <c r="F48" s="5" t="inlineStr">
+      <c r="F50" s="5" t="inlineStr">
         <is>
           <t>Currency of the client exhibits [required]</t>
         </is>
       </c>
-      <c r="G48" s="6" t="n"/>
+      <c r="G50" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:G2"/>
   </mergeCells>
-  <dataValidations count="12">
+  <dataValidations count="14">
     <dataValidation sqref="C14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"L,C,E"</formula1>
     </dataValidation>
@@ -2466,15 +2520,21 @@
       <formula1>"STANDALONE,PROGRAMME"</formula1>
     </dataValidation>
     <dataValidation sqref="C40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"LOGNORMAL,GAMMA,WEIBULL,PARETO,GPD"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"PYTHON,NATIVE"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"POISSON,NEGBIN"</formula1>
     </dataValidation>
-    <dataValidation sqref="C41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"EXPERIENCE,SCENARIOS,BOTH"</formula1>
     </dataValidation>
-    <dataValidation sqref="C44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C46" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"LOGNORMAL,NORMAL"</formula1>
     </dataValidation>
-    <dataValidation sqref="C48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"QUOTE,USD"</formula1>
     </dataValidation>
   </dataValidations>

--- a/excel/templates/XoL_Control.xlsx
+++ b/excel/templates/XoL_Control.xlsx
@@ -1217,7 +1217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1592,28 +1592,20 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>treaty_basis</t>
+          <t>ete_payer_filter</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Basis</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>RA</t>
-        </is>
-      </c>
+          <t>Mode</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n"/>
       <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>RA,LO</t>
-        </is>
-      </c>
+      <c r="E18" s="5" t="inlineStr"/>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>Risks attaching or losses occurring [required]</t>
+          <t>ETE / Merit only: comma list of payers (Payer Name) to include (blank = all; A16 flags several payers)</t>
         </is>
       </c>
       <c r="G18" s="6" t="n"/>
@@ -1621,7 +1613,7 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>claims_trigger</t>
+          <t>treaty_basis</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -1631,18 +1623,18 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>INCURRED</t>
+          <t>RA</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr"/>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>INCURRED,PAID</t>
+          <t>RA,LO</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>Claims date trigger [required]</t>
+          <t>Risks attaching or losses occurring [required]</t>
         </is>
       </c>
       <c r="G19" s="6" t="n"/>
@@ -1650,7 +1642,7 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>paid_runoff_months</t>
+          <t>claims_trigger</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -1658,16 +1650,20 @@
           <t>Basis</t>
         </is>
       </c>
-      <c r="C20" s="6" t="n"/>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>months</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr"/>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>INCURRED</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr"/>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>INCURRED,PAID</t>
+        </is>
+      </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>Paid trigger only: months after treaty year end</t>
+          <t>Claims date trigger [required]</t>
         </is>
       </c>
       <c r="G20" s="6" t="n"/>
@@ -1675,7 +1671,7 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>pp_accumulation</t>
+          <t>paid_runoff_months</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -1683,20 +1679,16 @@
           <t>Basis</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>POLICY_YEAR</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr"/>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>POLICY_YEAR,TREATY_YEAR</t>
-        </is>
-      </c>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>months</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr"/>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>Per-person accumulation period [required]</t>
+          <t>Paid trigger only: months after treaty year end</t>
         </is>
       </c>
       <c r="G21" s="6" t="n"/>
@@ -1704,24 +1696,28 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>epi_quote_year</t>
+          <t>pp_accumulation</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Exposure</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>quote ccy</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr"/>
+          <t>Basis</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>POLICY_YEAR</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr"/>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>POLICY_YEAR,TREATY_YEAR</t>
+        </is>
+      </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>Expected premium income for the quote year [required]</t>
+          <t>Per-person accumulation period [required]</t>
         </is>
       </c>
       <c r="G22" s="6" t="n"/>
@@ -1729,7 +1725,7 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>expected_lives_quote_year</t>
+          <t>epi_quote_year</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -1740,13 +1736,13 @@
       <c r="C23" s="6" t="n"/>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>lives</t>
+          <t>quote ccy</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr"/>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>Blank = EPI / trended average premium</t>
+          <t>Expected premium income for the quote year [required]</t>
         </is>
       </c>
       <c r="G23" s="6" t="n"/>
@@ -1754,24 +1750,24 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>years_included</t>
+          <t>expected_lives_quote_year</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Exposure</t>
         </is>
       </c>
       <c r="C24" s="6" t="n"/>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>years</t>
+          <t>lives</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr"/>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>Experience years used (comma list, 2-5 years) [required]</t>
+          <t>Blank = EPI / trended average premium</t>
         </is>
       </c>
       <c r="G24" s="6" t="n"/>
@@ -1779,7 +1775,7 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>output_threshold_pct_min_ap</t>
+          <t>years_included</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -1787,20 +1783,16 @@
           <t>Data</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
+      <c r="C25" s="6" t="n"/>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>years</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr"/>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>Write claimant rows above this % of the lowest AP [required]</t>
+          <t>Experience years used (comma list, 2-5 years) [required]</t>
         </is>
       </c>
       <c r="G25" s="6" t="n"/>
@@ -1808,7 +1800,7 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>policy_limit</t>
+          <t>output_threshold_pct_min_ap</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
@@ -1816,16 +1808,20 @@
           <t>Data</t>
         </is>
       </c>
-      <c r="C26" s="6" t="n"/>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>quote ccy</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr"/>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>Overall per-person policy limit (blank = none)</t>
+          <t>Write claimant rows above this % of the lowest AP [required]</t>
         </is>
       </c>
       <c r="G26" s="6" t="n"/>
@@ -1833,28 +1829,24 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>outlier_method</t>
+          <t>policy_limit</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Outliers</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>IQR</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr"/>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>VALUE,IQR,NONE</t>
-        </is>
-      </c>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>quote ccy</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr"/>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>Outlier threshold rule [required]</t>
+          <t>Overall per-person policy limit (blank = none)</t>
         </is>
       </c>
       <c r="G27" s="6" t="n"/>
@@ -1862,7 +1854,7 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>outlier_value</t>
+          <t>outlier_method</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
@@ -1870,16 +1862,20 @@
           <t>Outliers</t>
         </is>
       </c>
-      <c r="C28" s="6" t="n"/>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>quote ccy</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr"/>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>IQR</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr"/>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>VALUE,IQR,NONE</t>
+        </is>
+      </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>Threshold when outlier_method = VALUE</t>
+          <t>Outlier threshold rule [required]</t>
         </is>
       </c>
       <c r="G28" s="6" t="n"/>
@@ -1887,7 +1883,7 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>iqr_multiplier</t>
+          <t>outlier_value</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
@@ -1895,20 +1891,16 @@
           <t>Outliers</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
+      <c r="C29" s="6" t="n"/>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>quote ccy</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr"/>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>Multiplier when outlier_method = IQR</t>
+          <t>Threshold when outlier_method = VALUE</t>
         </is>
       </c>
       <c r="G29" s="6" t="n"/>
@@ -1916,28 +1908,28 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>full_cred_n</t>
+          <t>iqr_multiplier</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Credibility</t>
+          <t>Outliers</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>claims</t>
+          <t>x</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr"/>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>Claims for full credibility (workshop default 64) [required]</t>
+          <t>Multiplier when outlier_method = IQR</t>
         </is>
       </c>
       <c r="G30" s="6" t="n"/>
@@ -1945,7 +1937,7 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>complement_source</t>
+          <t>full_cred_n</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
@@ -1955,18 +1947,18 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>STOCHASTIC</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr"/>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>STOCHASTIC,BENCHMARK,EXPIRING</t>
-        </is>
-      </c>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>claims</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr"/>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>Credibility complement [required]</t>
+          <t>Claims for full credibility (workshop default 64) [required]</t>
         </is>
       </c>
       <c r="G31" s="6" t="n"/>
@@ -1974,7 +1966,7 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>benchmark_rate</t>
+          <t>complement_source</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
@@ -1982,16 +1974,20 @@
           <t>Credibility</t>
         </is>
       </c>
-      <c r="C32" s="6" t="n"/>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>quote ccy pppy</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr"/>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>STOCHASTIC</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr"/>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>STOCHASTIC,BENCHMARK,EXPIRING</t>
+        </is>
+      </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>When complement_source = BENCHMARK</t>
+          <t>Credibility complement [required]</t>
         </is>
       </c>
       <c r="G32" s="6" t="n"/>
@@ -1999,28 +1995,24 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>incidence_adj</t>
+          <t>benchmark_rate</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Incidence</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Credibility</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="n"/>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>quote ccy pppy</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr"/>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Overall incidence adjustment (1 = none); justify [required]</t>
+          <t>When complement_source = BENCHMARK</t>
         </is>
       </c>
       <c r="G33" s="6" t="n"/>
@@ -2028,12 +2020,12 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>qs_cedant_retention_pct</t>
+          <t>incidence_adj</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>QS</t>
+          <t>Incidence</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
@@ -2043,13 +2035,13 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>x</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr"/>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>Cedant retention under an existing QS (1 = no QS) [required]</t>
+          <t>Overall incidence adjustment (1 = none); justify [required]</t>
         </is>
       </c>
       <c r="G34" s="6" t="n"/>
@@ -2057,28 +2049,28 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>evaluate_mode</t>
+          <t>qs_cedant_retention_pct</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Programme</t>
+          <t>QS</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>STANDALONE</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr"/>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>STANDALONE,PROGRAMME</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr"/>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Options standalone, or stacked per Programme [required]</t>
+          <t>Cedant retention under an existing QS (1 = no QS) [required]</t>
         </is>
       </c>
       <c r="G35" s="6" t="n"/>
@@ -2086,28 +2078,28 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>iterations</t>
+          <t>evaluate_mode</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Stochastic</t>
+          <t>Programme</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>10000</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr"/>
+          <t>STANDALONE</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr"/>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>STANDALONE,PROGRAMME</t>
+        </is>
+      </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>Simulation iterations [required]</t>
+          <t>Options standalone, or stacked per Programme [required]</t>
         </is>
       </c>
       <c r="G36" s="6" t="n"/>
@@ -2115,7 +2107,7 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>iterations</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
@@ -2125,14 +2117,18 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>12345</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="inlineStr"/>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
       <c r="E37" s="5" t="inlineStr"/>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>Random seed (recorded in the run log) [required]</t>
+          <t>Simulation iterations [required]</t>
         </is>
       </c>
       <c r="G37" s="6" t="n"/>
@@ -2140,7 +2136,7 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>fit_cutoff</t>
+          <t>seed</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
@@ -2148,16 +2144,16 @@
           <t>Stochastic</t>
         </is>
       </c>
-      <c r="C38" s="6" t="n"/>
-      <c r="D38" s="5" t="inlineStr">
-        <is>
-          <t>quote ccy</t>
-        </is>
-      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>12345</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr"/>
       <c r="E38" s="5" t="inlineStr"/>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>Severity fitting cut-off (blank = AP)</t>
+          <t>Random seed (recorded in the run log) [required]</t>
         </is>
       </c>
       <c r="G38" s="6" t="n"/>
@@ -2165,7 +2161,7 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>fit_candidates</t>
+          <t>fit_cutoff</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
@@ -2173,16 +2169,16 @@
           <t>Stochastic</t>
         </is>
       </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>LOGNORMAL,GAMMA,WEIBULL,PARETO,GPD</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="inlineStr"/>
+      <c r="C39" s="6" t="n"/>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>quote ccy</t>
+        </is>
+      </c>
       <c r="E39" s="5" t="inlineStr"/>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>Candidate severity distributions [required]</t>
+          <t>Severity fitting cut-off (blank = AP)</t>
         </is>
       </c>
       <c r="G39" s="6" t="n"/>
@@ -2190,7 +2186,7 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>fit_selected</t>
+          <t>fit_candidates</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
@@ -2198,16 +2194,16 @@
           <t>Stochastic</t>
         </is>
       </c>
-      <c r="C40" s="6" t="n"/>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>LOGNORMAL,GAMMA,WEIBULL,PARETO,GPD</t>
+        </is>
+      </c>
       <c r="D40" s="5" t="inlineStr"/>
-      <c r="E40" s="5" t="inlineStr">
-        <is>
-          <t>LOGNORMAL,GAMMA,WEIBULL,PARETO,GPD</t>
-        </is>
-      </c>
+      <c r="E40" s="5" t="inlineStr"/>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>Severity distribution used by the simulation (blank = lowest AIC in stage 04a); justify an override</t>
+          <t>Candidate severity distributions [required]</t>
         </is>
       </c>
       <c r="G40" s="6" t="n"/>
@@ -2215,7 +2211,7 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>severity_source</t>
+          <t>fit_selected</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
@@ -2223,20 +2219,16 @@
           <t>Stochastic</t>
         </is>
       </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>PYTHON</t>
-        </is>
-      </c>
+      <c r="C41" s="6" t="n"/>
       <c r="D41" s="5" t="inlineStr"/>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>PYTHON,NATIVE</t>
+          <t>LOGNORMAL,GAMMA,WEIBULL,PARETO,GPD</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>PYTHON: distribution selected in 04a_fit_severity (Python tool); NATIVE: Pareto fitted in stage 04 (no Python) [required]</t>
+          <t>Severity distribution used by the simulation (blank = lowest AIC in stage 04a); justify an override</t>
         </is>
       </c>
       <c r="G41" s="6" t="n"/>
@@ -2244,7 +2236,7 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>freq_model</t>
+          <t>severity_source</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
@@ -2254,18 +2246,18 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>POISSON</t>
+          <t>PYTHON</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr"/>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>POISSON,NEGBIN</t>
+          <t>PYTHON,NATIVE</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>Frequency distribution [required]</t>
+          <t>PYTHON: distribution selected in 04a_fit_severity (Python tool); NATIVE: Pareto fitted in stage 04 (no Python) [required]</t>
         </is>
       </c>
       <c r="G42" s="6" t="n"/>
@@ -2273,7 +2265,7 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>ev_freq_source</t>
+          <t>freq_model</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
@@ -2283,18 +2275,18 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>BOTH</t>
+          <t>POISSON</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr"/>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>EXPERIENCE,SCENARIOS,BOTH</t>
+          <t>POISSON,NEGBIN</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Per-event simulation: historical events, EvScenarios (with a return period), or both [required]</t>
+          <t>Frequency distribution [required]</t>
         </is>
       </c>
       <c r="G43" s="6" t="n"/>
@@ -2302,7 +2294,7 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>sl_attritional_threshold</t>
+          <t>ev_freq_source</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
@@ -2312,18 +2304,18 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>100000</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="inlineStr">
-        <is>
-          <t>quote ccy</t>
-        </is>
-      </c>
-      <c r="E44" s="5" t="inlineStr"/>
+          <t>BOTH</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr"/>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>EXPERIENCE,SCENARIOS,BOTH</t>
+        </is>
+      </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>Stop loss: attritional / large split [required]</t>
+          <t>Per-event simulation: historical events, EvScenarios (with a return period), or both [required]</t>
         </is>
       </c>
       <c r="G44" s="6" t="n"/>
@@ -2331,7 +2323,7 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>sl_cov_floor</t>
+          <t>sl_attritional_threshold</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
@@ -2341,14 +2333,18 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="inlineStr"/>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>quote ccy</t>
+        </is>
+      </c>
       <c r="E45" s="5" t="inlineStr"/>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>Stop loss: minimum CoV of the attritional cost per life [required]</t>
+          <t>Stop loss: attritional / large split [required]</t>
         </is>
       </c>
       <c r="G45" s="6" t="n"/>
@@ -2356,7 +2352,7 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>sl_attritional_dist</t>
+          <t>sl_cov_floor</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
@@ -2366,18 +2362,14 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>LOGNORMAL</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr"/>
-      <c r="E46" s="5" t="inlineStr">
-        <is>
-          <t>LOGNORMAL,NORMAL</t>
-        </is>
-      </c>
+      <c r="E46" s="5" t="inlineStr"/>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>Stop loss: distribution of the attritional cost per life [required]</t>
+          <t>Stop loss: minimum CoV of the attritional cost per life [required]</t>
         </is>
       </c>
       <c r="G46" s="6" t="n"/>
@@ -2385,24 +2377,28 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>net_claims_budget</t>
+          <t>sl_attritional_dist</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Cedant impact</t>
-        </is>
-      </c>
-      <c r="C47" s="6" t="n"/>
-      <c r="D47" s="5" t="inlineStr">
-        <is>
-          <t>quote ccy</t>
-        </is>
-      </c>
-      <c r="E47" s="5" t="inlineStr"/>
+          <t>Stochastic</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>LOGNORMAL</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr"/>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>LOGNORMAL,NORMAL</t>
+        </is>
+      </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>Blank = best-estimate gross claims</t>
+          <t>Stop loss: distribution of the attritional cost per life [required]</t>
         </is>
       </c>
       <c r="G47" s="6" t="n"/>
@@ -2410,7 +2406,7 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>reference_lives</t>
+          <t>net_claims_budget</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
@@ -2421,13 +2417,13 @@
       <c r="C48" s="6" t="n"/>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>lives</t>
+          <t>quote ccy</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr"/>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>Blank = expected lives for the quote year</t>
+          <t>Blank = best-estimate gross claims</t>
         </is>
       </c>
       <c r="G48" s="6" t="n"/>
@@ -2435,7 +2431,7 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>return_periods</t>
+          <t>reference_lives</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
@@ -2443,20 +2439,16 @@
           <t>Cedant impact</t>
         </is>
       </c>
-      <c r="C49" s="6" t="inlineStr">
-        <is>
-          <t>5,50,250</t>
-        </is>
-      </c>
+      <c r="C49" s="6" t="n"/>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>years</t>
+          <t>lives</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr"/>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>Return periods shown in Exhibit C2 [required]</t>
+          <t>Blank = expected lives for the quote year</t>
         </is>
       </c>
       <c r="G49" s="6" t="n"/>
@@ -2464,31 +2456,60 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
+          <t>return_periods</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>Cedant impact</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>5,50,250</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr"/>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>Return periods shown in Exhibit C2 [required]</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
           <t>currency_display</t>
         </is>
       </c>
-      <c r="B50" s="5" t="inlineStr">
+      <c r="B51" s="5" t="inlineStr">
         <is>
           <t>Cedant impact</t>
         </is>
       </c>
-      <c r="C50" s="6" t="inlineStr">
+      <c r="C51" s="6" t="inlineStr">
         <is>
           <t>QUOTE</t>
         </is>
       </c>
-      <c r="D50" s="5" t="inlineStr"/>
-      <c r="E50" s="5" t="inlineStr">
+      <c r="D51" s="5" t="inlineStr"/>
+      <c r="E51" s="5" t="inlineStr">
         <is>
           <t>QUOTE,USD</t>
         </is>
       </c>
-      <c r="F50" s="5" t="inlineStr">
+      <c r="F51" s="5" t="inlineStr">
         <is>
           <t>Currency of the client exhibits [required]</t>
         </is>
       </c>
-      <c r="G50" s="6" t="n"/>
+      <c r="G51" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2501,40 +2522,40 @@
     <dataValidation sqref="C15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"GROSS,GROSSNET,NET"</formula1>
     </dataValidation>
-    <dataValidation sqref="C18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"RA,LO"</formula1>
     </dataValidation>
-    <dataValidation sqref="C19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"INCURRED,PAID"</formula1>
     </dataValidation>
-    <dataValidation sqref="C21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"POLICY_YEAR,TREATY_YEAR"</formula1>
     </dataValidation>
-    <dataValidation sqref="C27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"VALUE,IQR,NONE"</formula1>
     </dataValidation>
-    <dataValidation sqref="C31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"STOCHASTIC,BENCHMARK,EXPIRING"</formula1>
     </dataValidation>
-    <dataValidation sqref="C35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"STANDALONE,PROGRAMME"</formula1>
     </dataValidation>
-    <dataValidation sqref="C40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"LOGNORMAL,GAMMA,WEIBULL,PARETO,GPD"</formula1>
     </dataValidation>
-    <dataValidation sqref="C41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"PYTHON,NATIVE"</formula1>
     </dataValidation>
-    <dataValidation sqref="C42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"POISSON,NEGBIN"</formula1>
     </dataValidation>
-    <dataValidation sqref="C43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"EXPERIENCE,SCENARIOS,BOTH"</formula1>
     </dataValidation>
-    <dataValidation sqref="C46" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"LOGNORMAL,NORMAL"</formula1>
     </dataValidation>
-    <dataValidation sqref="C50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"QUOTE,USD"</formula1>
     </dataValidation>
   </dataValidations>
